--- a/data/art.xlsx
+++ b/data/art.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final + 치료센터 +예체능\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V5 -\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,759 +19,786 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="251">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="260">
+  <x:si>
+    <x:t>시흥시 정왕천로 411번길 62, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕대로117번길 32, 201호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 131-1, 3층(하중동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 수풀안길 22, 701~704호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대골안길 37, 1층 우측(대야동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 520, 동운디오빌 202호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 30, 503호, 507호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 능곡로 174, 603-604호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 83, 302~303호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 죽율로 38, 3층 301-302호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 비둘기공원7길 18, 505호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 능곡로 178, 501,502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 7, 305호, 306호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시흥대로1074번길 17-1, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계남로 12, 201-202호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 진말1로 10, 601-602호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 9, 5층 509호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길 3, 302호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로14번길 87, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로61, 202, 203호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 87, 베스트프라자 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로 74, 304,305호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길 3, 407호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길, 409호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로30번길 4, 204호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 207, 401-402호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계로 347, 501호,502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대골길 47-12, 1층 101호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길 3, 404호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 93, 303-304호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시청로 68번길 10, 504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 도일로 112번길 11, 1층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대중앙태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칸타빌레피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대스타태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(피아노, 기타)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대석사차오름태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 28, 은계디스퀘어 602, 607, 608호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로278번길 19-13, A-212-216호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTC태권도아카데미 충효도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2642-6055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-6272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-7929</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-3358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-7895</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-5580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-8890-5230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-8177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-1118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-0203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2697-1731</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 467 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-5535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4004-9324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카운터짐 합기도킥복싱MMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-307-0777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대명성체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시소뮤직실용음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTI국가대표태권스쿨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">위도 </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">배곧 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-8534</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로, 66-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 99, 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-1193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4871-6601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-0288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5038-7197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-316-3166</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1365-5474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-7776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-4909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1320-6088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-492-1243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-6262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1405-8711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-6676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4243-7853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2126-3443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 매화1로 3, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5335-1357</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-6312-5576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 호현로 69, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1343-7062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-8684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-403-6066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6741-3002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1317-9317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2232-5207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 128, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4544</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3943-1911</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6888-9776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-493-0033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1661</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-493-6788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-5505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-7100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1342-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비룡 T.M.A태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4545-9363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 199, 4층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6570-4787</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-6696</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-9104-3127</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(수영, 생존수영)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-3575</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-509-6677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1390-9982</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(가야금, 전통악기)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2168-2053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대 호돌이 태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-8917-8435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1998</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-7301-5325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-7778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5036-4810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 옥터로 34 101호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5112-7893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3159-9296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-4447</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 562-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3137-9547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-8801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-495-6101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5700-5554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-9597-5526</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1335-1695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5418-6922</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 시흥시 장곡동 949-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1446-0586</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-492-1579</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9924</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 86, 5층 504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점핑클럽 줄넘기 시흥 장현장곡센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 진말로 7, 205-206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 453-2, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대은로 8-10, 5층</x:t>
+  </x:si>
   <x:si>
     <x:t>예능(피아노, 드럼, 기타, 보컬)</x:t>
   </x:si>
   <x:si>
+    <x:t>시흥시 은계남로12, 208호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 95, 503호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 대골안길 24, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 신천1길 22-1, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 신천로19번길 8, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장곡로 74, 405호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 인선길 104, 201호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 함송로 24, 405호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 7, 302호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 중심상가로 287, 지층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 28, 606호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 황고개로 528, 705호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장곡동 802-1, 206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 504번길 1, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 9, 705호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 역전로 353, 210호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 178번지 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로 66-7, 401호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 매화2로48번길 13, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점프윙스줄넘기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으뜸음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>능곡태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혜성음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더뮤즈음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열정태권도장</x:t>
+  </x:si>
+  <x:si>
     <x:t>예능(피아노)</x:t>
   </x:si>
   <x:si>
+    <x:t>체육(농구)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메가스태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(줄넘기)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클라라음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무진태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대수태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시흥대로 1121, 304-305호(신천동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 마유로 416, 비101호(정왕동, 월드프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(미술)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천하태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNA미술학원</x:t>
+  </x:si>
+  <x:si>
     <x:t>셀라음악학원</x:t>
   </x:si>
   <x:si>
+    <x:t>안토음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씨앤씨미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연세대태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합기도 진중관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바르첼음악학원</x:t>
+  </x:si>
+  <x:si>
     <x:t>체육(태권도)</x:t>
   </x:si>
   <x:si>
+    <x:t>물방울국악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>놀작그림이야기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베스트태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YK태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>표경진음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태비태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키즈펀태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(합기도)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오아미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕호태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧충효태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장현미술교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕천로427번길 27-2, 201호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 승지로 60번길 25, 5층 502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 함송로 29번길 7, 401~402호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 106-25, 204~206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계중앙로 140, 네이처포레 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장현장곡로 65, s001동 107호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로115번길 17, 204-205호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 40, 5층 504-507호</x:t>
+  </x:si>
+  <x:si>
     <x:t>시흥시 남왕길 38, 5층 502, 503호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 승지로 60번길 25, 5층 502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계중앙로 140, 네이처포레 201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 106-25, 204~206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 40, 5층 504-507호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 함송로 29번길 7, 401~402호</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥시 배곧4로 103, 대경프라자 401호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 장현장곡로 65, s001동 107호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시흥대로 1121, 304-305호(신천동)</x:t>
+    <x:t>용인대성호태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대라온태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대왕호태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건국대신일체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대석사태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>국가대표태권스쿨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대이룸태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대장곡태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베스트금빛태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래태권도효교육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금강태권도효체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연세대솔내음태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뮤직플러스 음악교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩미술교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봄봄피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음을그리는미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대석사모란체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔젤크루키즈스위밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레인보우 음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더피아노 음악전문학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌드리더태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙벨트태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계명대 도일태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홍익이화태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>케이타이거즈은계도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대비전태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리아트클래스미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하늘빛음악미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루밍피아노음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주식회사 시흥비젼센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한양대매화태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한마루태권도라온관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행동 무진태권도장</x:t>
   </x:si>
   <x:si>
     <x:t>용인대홍익태권도장</x:t>
   </x:si>
   <x:si>
-    <x:t>완두콩미술교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한마루태권도라온관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봄봄피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시소뮤직실용음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대장곡태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대석사태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대석사차오름태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(피아노, 기타)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대이룸태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTI국가대표태권스쿨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대스타태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>국가대표태권스쿨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칸타빌레피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대왕호태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대명성체육관</x:t>
-  </x:si>
-  <x:si>
     <x:t>경희대석사체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행동 무진태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대중앙태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건국대신일체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뮤직플러스 음악교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베스트금빛태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마음을그리는미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래태권도효교육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5036-4810</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1320-6088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-8801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-492-1243</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-0288</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 옥터로 34 101호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5418-6922</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0312</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1365-5474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-7301-5325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3159-9296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1405-8711</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-492-1579</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-499-3575</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-509-6677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-4447</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-495-6101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-9924</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 하중로 199, 4층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5700-5554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-9597-5526</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4544</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-316-3166</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 시흥시 장곡동 949-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3137-9547</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-4909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1446-0586</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-6262</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4871-6601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-6676</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5112-7893</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-7778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1335-1695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 562-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1390-9982</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-6312-5576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6570-4787</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6741-3002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4853</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 호현로 69, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-8684</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2232-5207</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-6696</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1317-9317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5335-1357</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1343-7062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-9887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(수영, 생존수영)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 95, 503호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 역전로 353, 210호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 504번길 1, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로 66-7, 401호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1342-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6888-9776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-315-8534</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 함송로 24, 405호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열정태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합기도 진중관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연세대태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으뜸음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천하태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>표경진음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바르첼음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왕호태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오아미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키즈펀태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(미술)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(합기도)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혜성음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장현미술교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀작그림이야기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 마유로 416, 비101호(정왕동, 월드프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금강태권도효체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대비전태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레인보우 음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대석사모란체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주식회사 시흥비젼센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계명대 도일태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더피아노 음악전문학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대성호태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대라온태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하늘빛음악미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연세대솔내음태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루밍피아노음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블랙벨트태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌드리더태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-1193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-8917-8435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-493-0033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4545-9363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-403-6066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-9104-3127</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-7100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3943-1911</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2168-2053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-7776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5038-7197</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-307-0777</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-7929</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-5580</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(가야금, 전통악기)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-1118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 467 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1998</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2642-6055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-493-6788</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로, 66-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTC태권도아카데미 충효도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-7895</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-5535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4004-9324</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 99, 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-5505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YK태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물방울국악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧충효태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베스트태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>태비태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNA미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안토음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 수풀안길 22, 701~704호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 83, 302~303호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 30, 503호, 507호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로 74, 304,305호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로14번길 87, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-8890-5230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-315-3358</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">배곧 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리아트클래스미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한양대매화태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>케이타이거즈은계도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홍익이화태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔젤크루키즈스위밍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-8177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-0203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1661</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-6272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 매화1로 3, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 128, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대 호돌이 태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씨앤씨미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(농구)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대수태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더뮤즈음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점프윙스줄넘기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메가스태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무진태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(줄넘기)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클라라음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>능곡태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 중심상가로 287, 지층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 인선길 104, 201호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장곡동 802-1, 206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 매화2로48번길 13, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 신천1길 22-1, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 178번지 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 28, 606호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 9, 705호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 7, 302호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 신천로19번길 8, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 86, 5층 504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계남로12, 208호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 진말로 7, 205-206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 황고개로 528, 705호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 453-2, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 대골안길 24, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대은로 8-10, 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장곡로 74, 405호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 비둘기공원7길 18, 505호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 9, 5층 509호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계남로 12, 201-202호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시청로 68번길 10, 504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 520, 동운디오빌 202호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 하중로 131-1, 3층(하중동)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 93, 303-304호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 하중로 207, 401-402호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대골길 47-12, 1층 101호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 7, 305호, 306호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 죽율로 38, 3층 301-302호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕천로 411번길 62, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 능곡로 178, 501,502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대골안길 37, 1층 우측(대야동)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 능곡로 174, 603-604호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 도일로 112번길 11, 1층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕대로117번길 32, 201호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 407호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 87, 베스트프라자 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로61, 202, 203호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 302호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시흥대로1074번길 17-1, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계로 347, 501호,502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로30번길 4, 204호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길, 409호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 404호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 28, 은계디스퀘어 602, 607, 608호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로278번길 19-13, A-212-216호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분야</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">위도 </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -779,62 +806,213 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fonts count="11">
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="함초롬돋움"/>
-      <x:sz val="8"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="8"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="함초롬돋움"/>
-      <x:sz val="8"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="8"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="함초롬돋움"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="함초롬돋움"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="함초롬돋움"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="함초롬돋움"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="8"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -870,23 +1048,23 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="bottom"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="bottom"/>
         </x:xf>
       </mc:Fallback>
@@ -900,19 +1078,6 @@
       </mc:Choice>
       <mc:Fallback>
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="bottom"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="bottom"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="bottom"/>
         </x:xf>
       </mc:Fallback>
@@ -943,16 +1108,440 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom" shrinkToFit="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="bottom" shrinkToFit="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
-  <x:dxfs/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
 </file>
 
@@ -1155,7 +1744,7 @@
   <x:sheetPr codeName="Sheet1">
     <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G77"/>
+  <x:dimension ref="A1:G80"/>
   <x:sheetFormatPr defaultColWidth="12.62890625" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="22.75" style="6" customWidth="1"/>
@@ -1167,42 +1756,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A1" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>250</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>248</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A2" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>200</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>176</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F2">
         <x:v>37.446509734139703</x:v>
@@ -1213,19 +1802,19 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A3" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F3">
         <x:v>37.415613493757398</x:v>
@@ -1236,19 +1825,19 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A4" s="3" t="s">
-        <x:v>181</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>210</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F4">
         <x:v>37.447524060199498</x:v>
@@ -1259,19 +1848,19 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A5" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F5">
         <x:v>37.4444172059004</x:v>
@@ -1282,19 +1871,19 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A6" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F6">
         <x:v>37.439140760562097</x:v>
@@ -1305,19 +1894,19 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A7" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F7">
         <x:v>37.439654117607503</x:v>
@@ -1328,19 +1917,19 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A8" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F8">
         <x:v>37.447497932590402</x:v>
@@ -1351,19 +1940,19 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A9" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>203</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>37.4370981790032</x:v>
@@ -1374,19 +1963,19 @@
     </x:row>
     <x:row r="10" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A10" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>180</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>37.442450802593598</x:v>
@@ -1397,19 +1986,19 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A11" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F11">
         <x:v>37.440203699999998</x:v>
@@ -1420,19 +2009,19 @@
     </x:row>
     <x:row r="12" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A12" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>205</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F12">
         <x:v>37.439262473807098</x:v>
@@ -1443,19 +2032,19 @@
     </x:row>
     <x:row r="13" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A13" s="3" t="s">
-        <x:v>102</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F13">
         <x:v>37.4440801889331</x:v>
@@ -1466,19 +2055,19 @@
     </x:row>
     <x:row r="14" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A14" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>234</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F14">
         <x:v>37.431722871687697</x:v>
@@ -1489,19 +2078,19 @@
     </x:row>
     <x:row r="15" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A15" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>221</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F15">
         <x:v>37.446756841770203</x:v>
@@ -1512,19 +2101,19 @@
     </x:row>
     <x:row r="16" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A16" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>211</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F16">
         <x:v>37.439467125902802</x:v>
@@ -1535,19 +2124,19 @@
     </x:row>
     <x:row r="17" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A17" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F17">
         <x:v>37.436520158622002</x:v>
@@ -1558,19 +2147,19 @@
     </x:row>
     <x:row r="18" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A18" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F18">
         <x:v>37.437470952943301</x:v>
@@ -1581,19 +2170,19 @@
     </x:row>
     <x:row r="19" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A19" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F19">
         <x:v>37.437470952943301</x:v>
@@ -1604,19 +2193,19 @@
     </x:row>
     <x:row r="20" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A20" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>198</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F20">
         <x:v>37.415730984604401</x:v>
@@ -1627,19 +2216,19 @@
     </x:row>
     <x:row r="21" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A21" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>235</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F21">
         <x:v>37.449990132468002</x:v>
@@ -1650,19 +2239,19 @@
     </x:row>
     <x:row r="22" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A22" s="3" t="s">
-        <x:v>172</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>222</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>37.4370981790032</x:v>
@@ -1673,19 +2262,19 @@
     </x:row>
     <x:row r="23" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A23" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F23">
         <x:v>37.446258234266701</x:v>
@@ -1696,19 +2285,19 @@
     </x:row>
     <x:row r="24" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A24" s="3" t="s">
-        <x:v>173</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F24">
         <x:v>37.436555875625103</x:v>
@@ -1719,19 +2308,19 @@
     </x:row>
     <x:row r="25" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A25" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>206</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F25">
         <x:v>37.435910670723203</x:v>
@@ -1742,19 +2331,19 @@
     </x:row>
     <x:row r="26" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A26" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F26">
         <x:v>37.433101325125101</x:v>
@@ -1765,19 +2354,19 @@
     </x:row>
     <x:row r="27" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A27" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C27" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F27">
         <x:v>37.435575200000002</x:v>
@@ -1788,19 +2377,19 @@
     </x:row>
     <x:row r="28" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A28" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C28" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>244</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F28">
         <x:v>37.436520158622002</x:v>
@@ -1811,19 +2400,19 @@
     </x:row>
     <x:row r="29" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A29" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F29">
         <x:v>37.435539800000001</x:v>
@@ -1834,19 +2423,19 @@
     </x:row>
     <x:row r="30" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A30" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>226</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F30">
         <x:v>37.446271856574498</x:v>
@@ -1855,1089 +2444,1158 @@
         <x:v>126.788781442071</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:7" ht="13.19999999999999928946">
+    <x:row r="31" spans="1:7" customFormat="1" ht="13.19999999999999928946">
       <x:c r="A31" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="C31" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="s">
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F31">
-        <x:v>37.379756994823801</x:v>
+        <x:v>37.441218999999997</x:v>
       </x:c>
       <x:c r="G31">
-        <x:v>126.780655231343</x:v>
+        <x:v>126.79591720000001</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A32" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F32">
-        <x:v>37.380935743665098</x:v>
+        <x:v>37.379756994823801</x:v>
       </x:c>
       <x:c r="G32">
-        <x:v>126.800838255491</x:v>
+        <x:v>126.780655231343</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A33" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F33">
-        <x:v>37.393987258770103</x:v>
+        <x:v>37.380935743665098</x:v>
       </x:c>
       <x:c r="G33">
-        <x:v>126.80502098617799</x:v>
+        <x:v>126.800838255491</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A34" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F34">
-        <x:v>37.377924598191797</x:v>
+        <x:v>37.393987258770103</x:v>
       </x:c>
       <x:c r="G34">
-        <x:v>126.789234977478</x:v>
+        <x:v>126.80502098617799</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A35" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F35">
-        <x:v>37.383095058258597</x:v>
+        <x:v>37.377924598191797</x:v>
       </x:c>
       <x:c r="G35">
-        <x:v>126.793439976225</x:v>
+        <x:v>126.789234977478</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A36" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="C36" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="s">
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F36">
-        <x:v>37.3681299</x:v>
+        <x:v>37.383095058258597</x:v>
       </x:c>
       <x:c r="G36">
-        <x:v>126.8114073</x:v>
+        <x:v>126.793439976225</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A37" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C37" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>197</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F37">
-        <x:v>37.3797719285173</x:v>
+        <x:v>37.3681299</x:v>
       </x:c>
       <x:c r="G37">
-        <x:v>126.78044845216699</x:v>
+        <x:v>126.8114073</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A38" s="3" t="s">
-        <x:v>194</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C38" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F38">
-        <x:v>37.367986885096599</x:v>
+        <x:v>37.3797719285173</x:v>
       </x:c>
       <x:c r="G38">
-        <x:v>126.812257433445</x:v>
+        <x:v>126.78044845216699</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A39" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>196</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F39">
-        <x:v>37.3802217702235</x:v>
+        <x:v>37.367986885096599</x:v>
       </x:c>
       <x:c r="G39">
-        <x:v>126.78018496540599</x:v>
+        <x:v>126.812257433445</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A40" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C40" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D40" s="3" t="s">
-        <x:v>227</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E40" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F40">
-        <x:v>37.368047900000001</x:v>
+        <x:v>37.3802217702235</x:v>
       </x:c>
       <x:c r="G40">
-        <x:v>126.8117333</x:v>
+        <x:v>126.78018496540599</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A41" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C41" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D41" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E41" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F41">
-        <x:v>37.373484639470199</x:v>
+        <x:v>37.368047900000001</x:v>
       </x:c>
       <x:c r="G41">
-        <x:v>126.790663834062</x:v>
+        <x:v>126.8117333</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A42" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D42" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E42" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F42">
-        <x:v>37.398895451269198</x:v>
+        <x:v>37.373484639470199</x:v>
       </x:c>
       <x:c r="G42">
-        <x:v>126.800842012567</x:v>
+        <x:v>126.790663834062</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A43" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D43" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E43" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F43">
-        <x:v>37.3780517</x:v>
+        <x:v>37.398895451269198</x:v>
       </x:c>
       <x:c r="G43">
-        <x:v>126.7851359</x:v>
+        <x:v>126.800842012567</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A44" s="3" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B44" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C44" s="4" t="s">
-        <x:v>192</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E44" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F44">
-        <x:v>37.393291300000001</x:v>
+        <x:v>37.3780517</x:v>
       </x:c>
       <x:c r="G44">
-        <x:v>126.8054911</x:v>
+        <x:v>126.7851359</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A45" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C45" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="s">
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D45" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E45" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F45">
-        <x:v>37.343853763697801</x:v>
+        <x:v>37.393291300000001</x:v>
       </x:c>
       <x:c r="G45">
-        <x:v>126.78488703044</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7" ht="13.19999999999999928946">
-      <x:c r="A46" s="3" t="s">
-        <x:v>190</x:v>
+        <x:v>126.8054911</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7" customFormat="1" ht="13.19999999999999928946">
+      <x:c r="A46" s="7" t="s">
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B46" s="2" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C46" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="s">
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D46" s="3" t="s">
-        <x:v>195</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F46">
-        <x:v>37.3391834476597</x:v>
+        <x:v>37.377511200000001</x:v>
       </x:c>
       <x:c r="G46">
-        <x:v>126.74505684064501</x:v>
+        <x:v>126.7897158</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A47" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B47" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C47" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D47" s="3" t="s">
-        <x:v>223</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E47" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F47">
-        <x:v>37.348040523451701</x:v>
+        <x:v>37.343853763697801</x:v>
       </x:c>
       <x:c r="G47">
-        <x:v>126.761281592611</x:v>
+        <x:v>126.78488703044</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A48" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B48" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C48" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E48" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F48">
-        <x:v>37.363216527590602</x:v>
+        <x:v>37.3391834476597</x:v>
       </x:c>
       <x:c r="G48">
-        <x:v>126.73038793366599</x:v>
+        <x:v>126.74505684064501</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A49" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B49" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C49" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E49" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F49">
-        <x:v>37.3449460010808</x:v>
+        <x:v>37.348040523451701</x:v>
       </x:c>
       <x:c r="G49">
-        <x:v>126.78454647391</x:v>
+        <x:v>126.761281592611</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A50" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F50">
-        <x:v>37.344975648325899</x:v>
+        <x:v>37.363216527590602</x:v>
       </x:c>
       <x:c r="G50">
-        <x:v>126.691667263957</x:v>
+        <x:v>126.73038793366599</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A51" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D51" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F51">
-        <x:v>37.363914399999999</x:v>
+        <x:v>37.3449460010808</x:v>
       </x:c>
       <x:c r="G51">
-        <x:v>126.7313666</x:v>
+        <x:v>126.78454647391</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A52" s="3" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B52" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C52" s="3" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B52" s="2" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C52" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="D52" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F52">
-        <x:v>37.347775104464098</x:v>
+        <x:v>37.344975648325899</x:v>
       </x:c>
       <x:c r="G52">
-        <x:v>126.74652330961401</x:v>
+        <x:v>126.691667263957</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A53" s="3" t="s">
-        <x:v>188</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D53" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F53">
-        <x:v>37.340606096953202</x:v>
+        <x:v>37.363914399999999</x:v>
       </x:c>
       <x:c r="G53">
-        <x:v>126.785184851083</x:v>
+        <x:v>126.7313666</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A54" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C54" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D54" s="3" t="s">
-        <x:v>229</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F54">
-        <x:v>37.354204055025598</x:v>
+        <x:v>37.347775104464098</x:v>
       </x:c>
       <x:c r="G54">
-        <x:v>126.731510609651</x:v>
+        <x:v>126.74652330961401</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A55" s="3" t="s">
-        <x:v>116</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C55" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C55" s="3" t="s">
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D55" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E55" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F55">
-        <x:v>37.351623224076903</x:v>
+        <x:v>37.340606096953202</x:v>
       </x:c>
       <x:c r="G55">
-        <x:v>126.741285900721</x:v>
+        <x:v>126.785184851083</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A56" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C56" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D56" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E56" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F56">
-        <x:v>37.356434831380703</x:v>
+        <x:v>37.354204055025598</x:v>
       </x:c>
       <x:c r="G56">
-        <x:v>126.735558097655</x:v>
+        <x:v>126.731510609651</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A57" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C57" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D57" s="3" t="s">
-        <x:v>143</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E57" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F57">
-        <x:v>37.3479288939809</x:v>
+        <x:v>37.351623224076903</x:v>
       </x:c>
       <x:c r="G57">
-        <x:v>126.78274549352</x:v>
+        <x:v>126.741285900721</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A58" s="3" t="s">
-        <x:v>185</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B58" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C58" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C58" s="4" t="s">
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D58" s="3" t="s">
-        <x:v>230</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E58" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F58">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.356434831380703</x:v>
       </x:c>
       <x:c r="G58">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.735558097655</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A59" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B59" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C59" s="4" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E59" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F59">
+        <x:v>37.3479288939809</x:v>
+      </x:c>
+      <x:c r="G59">
+        <x:v>126.78274549352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:7" customFormat="1" ht="13.19999999999999928946">
+      <x:c r="A60" s="3" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B59" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C59" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D59" s="3" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F59">
-        <x:v>37.3821400563113</x:v>
-      </x:c>
-      <x:c r="G59">
-        <x:v>126.73471959141401</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:7" ht="13.19999999999999928946">
-      <x:c r="A60" s="3" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="B60" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C60" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C60" s="4" t="s">
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D60" s="3" t="s">
-        <x:v>231</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E60" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F60">
-        <x:v>37.374597699315999</x:v>
+        <x:v>37.346961604063502</x:v>
       </x:c>
       <x:c r="G60">
-        <x:v>126.73340139468</x:v>
+        <x:v>37.346961604063502</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A61" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B61" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D61" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E61" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F61">
-        <x:v>37.388653900000001</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G61">
-        <x:v>126.7383327</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A62" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B62" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C62" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D62" s="3" t="s">
-        <x:v>233</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E62" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F62">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.3821400563113</x:v>
       </x:c>
       <x:c r="G62">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.73471959141401</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A63" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B63" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C63" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D63" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E63" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F63">
-        <x:v>37.387693446987001</x:v>
+        <x:v>37.374597699315999</x:v>
       </x:c>
       <x:c r="G63">
-        <x:v>126.742398261746</x:v>
+        <x:v>126.73340139468</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A64" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B64" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C64" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D64" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D64" s="5" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E64" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F64">
-        <x:v>37.374245882999702</x:v>
+        <x:v>37.388653900000001</x:v>
       </x:c>
       <x:c r="G64">
-        <x:v>126.733976285898</x:v>
+        <x:v>126.7383327</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A65" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B65" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D65" s="3" t="s">
-        <x:v>237</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E65" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F65">
-        <x:v>37.390598400000002</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G65">
-        <x:v>126.73915220000001</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A66" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B66" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D66" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E66" s="3" t="s">
-        <x:v>151</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F66">
-        <x:v>37.374066672514303</x:v>
+        <x:v>37.387693446987001</x:v>
       </x:c>
       <x:c r="G66">
-        <x:v>126.734258152593</x:v>
+        <x:v>126.742398261746</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A67" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B67" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D67" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E67" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F67">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.374245882999702</x:v>
       </x:c>
       <x:c r="G67">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.733976285898</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A68" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D68" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E68" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F68">
-        <x:v>37.3748395</x:v>
+        <x:v>37.390598400000002</x:v>
       </x:c>
       <x:c r="G68">
-        <x:v>126.7329841</x:v>
+        <x:v>126.73915220000001</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A69" s="3" t="s">
-        <x:v>122</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B69" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C69" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="s">
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D69" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E69" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F69">
-        <x:v>37.377342450217498</x:v>
+        <x:v>37.374066672514303</x:v>
       </x:c>
       <x:c r="G69">
-        <x:v>126.727496126419</x:v>
+        <x:v>126.734258152593</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A70" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B70" s="2" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C70" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="s">
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D70" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E70" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F70">
-        <x:v>37.373859521094502</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G70">
-        <x:v>126.734576357199</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A71" s="3" t="s">
-        <x:v>159</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B71" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C71" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D71" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E71" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F71">
-        <x:v>37.3821400563113</x:v>
+        <x:v>37.3748395</x:v>
       </x:c>
       <x:c r="G71">
-        <x:v>126.73471959141401</x:v>
+        <x:v>126.7329841</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A72" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B72" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C72" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D72" s="3" t="s">
-        <x:v>164</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E72" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F72">
-        <x:v>37.382286000000001</x:v>
+        <x:v>37.377342450217498</x:v>
       </x:c>
       <x:c r="G72">
-        <x:v>126.7353871</x:v>
+        <x:v>126.727496126419</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A73" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B73" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C73" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D73" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E73" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F73">
-        <x:v>37.370413200000002</x:v>
+        <x:v>37.373859521094502</x:v>
       </x:c>
       <x:c r="G73">
-        <x:v>126.7339216</x:v>
+        <x:v>126.734576357199</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A74" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B74" s="2" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C74" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="s">
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D74" s="3" t="s">
-        <x:v>165</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E74" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F74">
-        <x:v>37.393791434243496</x:v>
+        <x:v>37.3821400563113</x:v>
       </x:c>
       <x:c r="G74">
-        <x:v>126.73934252606</x:v>
+        <x:v>126.73471959141401</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A75" s="3" t="s">
-        <x:v>156</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B75" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C75" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D75" s="3" t="s">
-        <x:v>245</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E75" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F75">
-        <x:v>37.3705044199436</x:v>
+        <x:v>37.382286000000001</x:v>
       </x:c>
       <x:c r="G75">
-        <x:v>126.72797063404801</x:v>
+        <x:v>126.7353871</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A76" s="3" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B76" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C76" s="4" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D76" s="3" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="E76" s="3" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B76" s="2" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C76" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D76" s="3" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="E76" s="3" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="F76">
-        <x:v>37.381190099999998</x:v>
+        <x:v>37.370413200000002</x:v>
       </x:c>
       <x:c r="G76">
-        <x:v>126.86278299999999</x:v>
+        <x:v>126.7339216</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A77" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C77" s="4" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D77" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E77" s="3" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F77">
+        <x:v>37.393791434243496</x:v>
+      </x:c>
+      <x:c r="G77">
+        <x:v>126.73934252606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:7" ht="13.19999999999999928946">
+      <x:c r="A78" s="3" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B78" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C78" s="4" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D78" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E78" s="3" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F78">
+        <x:v>37.3705044199436</x:v>
+      </x:c>
+      <x:c r="G78">
+        <x:v>126.72797063404801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:7" ht="13.19999999999999928946">
+      <x:c r="A79" s="3" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B79" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C79" s="3" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D79" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D77" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E77" s="3" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F77">
+      <x:c r="E79" s="3" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F79">
+        <x:v>37.381190099999998</x:v>
+      </x:c>
+      <x:c r="G79">
+        <x:v>126.86278299999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:7" ht="13.19999999999999928946">
+      <x:c r="A80" s="3" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B80" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C80" s="4" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D80" s="3" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E80" s="3" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F80">
         <x:v>37.382772633833603</x:v>
       </x:c>
-      <x:c r="G77">
+      <x:c r="G80">
         <x:v>126.86169881025801</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/art.xlsx
+++ b/data/art.xlsx
@@ -19,786 +19,777 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="260">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="257">
+  <x:si>
+    <x:t>031-319-7929</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-7895</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-6262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(수영, 생존수영)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-495-6101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-316-3166</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4545-9363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1320-6088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대 호돌이 태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-4909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3137-9547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-5505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-8890-5230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-1118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-3575</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1661</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YK태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무진태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열정태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>놀작그림이야기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점프윙스줄넘기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합기도 진중관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오아미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물방울국악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베스트태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(줄넘기)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNA미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>표경진음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혜성음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장현미술교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕호태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메가스태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>셀라음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태비태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(피아노)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키즈펀태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연세대태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(합기도)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안토음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧충효태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클라라음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으뜸음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(태권도)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육(농구)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>능곡태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(미술)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씨앤씨미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천하태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바르첼음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5038-7197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 99, 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-6696</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-6272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6741-3002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 남왕길 38, 5층 502, 503호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 승지로 60번길 25, 5층 502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 103, 대경프라자 401호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 함송로 29번길 7, 401~402호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계중앙로 140, 네이처포레 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장현장곡로 65, s001동 107호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4544</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1342-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-8534</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3943-1911</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(가야금, 전통악기)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시흥대로 1121, 304-305호(신천동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2232-5207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-315-3358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-8801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 진말로 7, 205-206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(피아노, 드럼, 기타, 보컬)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 95, 503호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 28, 606호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 신천로19번길 8, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 9, 705호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점핑클럽 줄넘기 시흥 장현장곡센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 중심상가로 287, 지층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 인선길 104, 201호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 178번지 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 매화2로48번길 13, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 86, 5층 504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계남로12, 208호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대은로 8-10, 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 504번길 1, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-1998</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1446-0586</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-5535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-493-6788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-7778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-0288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-492-1579</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4871-6601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 199, 4층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1365-5474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 128, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 7, 302호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 역전로 353, 210호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 함송로 24, 405호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 신천1길 22-1, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로 66-7, 401호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 황고개로 528, 705호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장곡동 802-1, 206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로278번길 19-13, A-212-216호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장곡로 74, 405호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 대골안길 24, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 453-2, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로, 66-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-0203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-9597-5526</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-403-6066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6570-4787</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 매화1로 3, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5036-4810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2126-3443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2697-1731</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4243-7853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5112-7893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-493-0033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-4004-9324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-8917-8435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 옥터로 34 101호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카운터짐 합기도킥복싱MMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 시흥시 장곡동 949-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비룡 T.M.A태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 대야동 562-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대석사모란체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔젤크루키즈스위밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리아트클래스미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행동 무진태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금강태권도효체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대스타태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>케이타이거즈은계도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예능(피아노, 기타)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레인보우 음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시소뮤직실용음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대이룸태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루밍피아노음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하늘빛음악미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뮤직플러스 음악교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봄봄피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대석사차오름태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계명대 도일태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렌드리더태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>국가대표태권스쿨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더피아노 음악전문학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한양대매화태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대왕호태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한마루태권도라온관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주식회사 시흥비젼센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홍익이화태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대중앙태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연세대솔내음태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베스트금빛태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대석사태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래태권도효교육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칸타빌레피아노교습소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대명성체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대홍익태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대석사체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙벨트태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTI국가대표태권스쿨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대비전태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대장곡태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 도일로 112번길 11, 1층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 131-1, 3층(하중동)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길, 409호</x:t>
+  </x:si>
   <x:si>
     <x:t>시흥시 정왕천로 411번길 62, 3층</x:t>
   </x:si>
   <x:si>
+    <x:t>시흥시 은계번영길 9, 5층 509호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 능곡로 174, 603-604호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길 3, 407호</x:t>
+  </x:si>
+  <x:si>
     <x:t>시흥시 정왕대로117번길 32, 201호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 하중로 131-1, 3층(하중동)</x:t>
+    <x:t>시흥시 대골길 47-12, 1층 101호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 93, 303-304호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시청로 68번길 10, 504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계로 347, 501호,502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로14번길 87, 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 7, 305호, 306호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 30, 503호, 507호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 87, 베스트프라자 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 월곶중앙로 70번길 3, 302호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 520, 동운디오빌 202호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 207, 401-402호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 83, 302~303호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계남로 12, 201-202호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 능곡로 178, 501,502호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 비둘기공원7길 18, 505호</x:t>
   </x:si>
   <x:si>
     <x:t>시흥시 수풀안길 22, 701~704호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 대골안길 37, 1층 우측(대야동)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 520, 동운디오빌 202호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 30, 503호, 507호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 능곡로 174, 603-604호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 83, 302~303호</x:t>
+    <x:t>시흥시 월곶중앙로 70번길 3, 404호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧5로 74, 304,305호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕천로427번길 27-2, 201호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 40, 5층 504-507호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 106-25, 204~206호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로115번길 17, 204-205호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더뮤즈음악학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대수태권도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-8177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5700-5554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-1193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-6676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-6312-5576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-4853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-4447</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5418-6922</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-9104-3127</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-5580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-492-1243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-509-6677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-3159-9296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 군자로 467 2층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1343-7062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1390-9982</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-8684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2642-6055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-7776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1405-8711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-5335-1357</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1317-9317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 호현로 69, 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTC태권도아카데미 충효도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-6888-9776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-307-0777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010-2168-2053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9924</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-7100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0507-1335-1695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 마유로 416, 비101호(정왕동, 월드프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음을그리는미술학원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건국대신일체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경희대라온태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용인대성호태권도장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 28, 은계디스퀘어 602, 607, 608호</x:t>
   </x:si>
   <x:si>
     <x:t>시흥시 죽율로 38, 3층 301-302호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 비둘기공원7길 18, 505호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 능곡로 178, 501,502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 7, 305호, 306호</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥시 시흥대로1074번길 17-1, 2층</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 은계남로 12, 201-202호</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥시 진말1로 10, 601-602호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 은계번영길 9, 5층 509호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 302호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로14번길 87, 2층</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥시 월곶중앙로61, 202, 203호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 배곧4로 87, 베스트프라자 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로 74, 304,305호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 407호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길, 409호</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥시 월곶중앙로30번길 4, 204호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 하중로 207, 401-402호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계로 347, 501호,502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대골길 47-12, 1층 101호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 월곶중앙로 70번길 3, 404호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 93, 303-304호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시청로 68번길 10, 504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 도일로 112번길 11, 1층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대중앙태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칸타빌레피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대스타태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(피아노, 기타)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대석사차오름태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 28, 은계디스퀘어 602, 607, 608호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로278번길 19-13, A-212-216호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTC태권도아카데미 충효도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2642-6055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-6272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-7929</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-315-3358</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-7895</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-5580</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-8890-5230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-8177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-1118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-0203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2697-1731</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 467 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-5535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4004-9324</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카운터짐 합기도킥복싱MMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-307-0777</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대명성체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시소뮤직실용음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTI국가대표태권스쿨</x:t>
-  </x:si>
-  <x:si>
     <x:t>지역구</x:t>
   </x:si>
   <x:si>
+    <x:t>분야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">위도 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성</x:t>
+  </x:si>
+  <x:si>
     <x:t>소래</x:t>
   </x:si>
   <x:si>
     <x:t>배곧</x:t>
   </x:si>
   <x:si>
-    <x:t>기관명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연락처</x:t>
+    <x:t xml:space="preserve">배곧 </x:t>
   </x:si>
   <x:si>
     <x:t>목감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">위도 </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">배곧 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-315-8534</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로, 66-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 99, 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-1193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4871-6601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-0288</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5038-7197</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-316-3166</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1365-5474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-7776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-4909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1320-6088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-492-1243</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-6262</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1405-8711</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-6676</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4243-7853</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2126-3443</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 매화1로 3, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0312</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5335-1357</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-6312-5576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 호현로 69, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1343-7062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-8684</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-403-6066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6741-3002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1317-9317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2232-5207</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 128, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4544</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3943-1911</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6888-9776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-9887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-493-0033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1661</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-493-6788</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4853</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-5505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-7100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1342-2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비룡 T.M.A태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-4545-9363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 하중로 199, 4층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-6570-4787</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-6696</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-9104-3127</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(수영, 생존수영)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-499-3575</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-509-6677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1390-9982</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(가야금, 전통악기)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-2168-2053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대 호돌이 태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-8917-8435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-1998</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-7301-5325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-7778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5036-4810</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 옥터로 34 101호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5112-7893</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3159-9296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-4447</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 562-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-3137-9547</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-8801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-495-6101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5700-5554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-4915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-9597-5526</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1335-1695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010-5418-6922</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 시흥시 장곡동 949-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0507-1446-0586</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-492-1579</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-9924</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 86, 5층 504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점핑클럽 줄넘기 시흥 장현장곡센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 진말로 7, 205-206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 453-2, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대은로 8-10, 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(피아노, 드럼, 기타, 보컬)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계남로12, 208호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 95, 503호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 대야동 대골안길 24, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 신천1길 22-1, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 신천로19번길 8, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장곡로 74, 405호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 인선길 104, 201호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 함송로 24, 405호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 7, 302호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 중심상가로 287, 지층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 28, 606호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 황고개로 528, 705호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장곡동 802-1, 206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 군자로 504번길 1, 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 9, 705호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 역전로 353, 210호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 178번지 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧5로 66-7, 401호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 매화2로48번길 13, 2층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점프윙스줄넘기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으뜸음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>능곡태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혜성음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더뮤즈음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열정태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(피아노)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(농구)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메가스태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(줄넘기)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클라라음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무진태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대수태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시흥대로 1121, 304-305호(신천동)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 마유로 416, 비101호(정왕동, 월드프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예능(미술)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천하태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNA미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>셀라음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안토음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씨앤씨미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연세대태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합기도 진중관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바르첼음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(태권도)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물방울국악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀작그림이야기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베스트태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YK태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>표경진음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>태비태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키즈펀태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육(합기도)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오아미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왕호태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧충효태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장현미술교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕천로427번길 27-2, 201호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 승지로 60번길 25, 5층 502호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 함송로 29번길 7, 401~402호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 106-25, 204~206호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계중앙로 140, 네이처포레 201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장현장곡로 65, s001동 107호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로115번길 17, 204-205호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 40, 5층 504-507호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 남왕길 38, 5층 502, 503호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 103, 대경프라자 401호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대성호태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대라온태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대왕호태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건국대신일체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대석사태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>국가대표태권스쿨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대이룸태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대장곡태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베스트금빛태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래태권도효교육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금강태권도효체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연세대솔내음태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뮤직플러스 음악교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩미술교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봄봄피아노교습소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마음을그리는미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대석사모란체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔젤크루키즈스위밍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레인보우 음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더피아노 음악전문학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렌드리더태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블랙벨트태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계명대 도일태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홍익이화태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>케이타이거즈은계도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대비전태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리아트클래스미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하늘빛음악미술학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루밍피아노음악학원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주식회사 시흥비젼센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한양대매화태권도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한마루태권도라온관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행동 무진태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용인대홍익태권도장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경희대석사체육관</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1148,7 +1139,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1231,7 +1221,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1266,7 +1255,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1311,7 +1299,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1355,7 +1342,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1440,7 +1426,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1461,7 +1446,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1492,7 +1476,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1744,7 +1727,7 @@
   <x:sheetPr codeName="Sheet1">
     <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G80"/>
+  <x:dimension ref="A1:G79"/>
   <x:sheetFormatPr defaultColWidth="12.62890625" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="22.75" style="6" customWidth="1"/>
@@ -1756,42 +1739,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A1" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>71</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>69</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A2" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>172</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F2">
         <x:v>37.446509734139703</x:v>
@@ -1802,19 +1785,19 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A3" s="3" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="F3">
         <x:v>37.415613493757398</x:v>
@@ -1825,19 +1808,19 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A4" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F4">
         <x:v>37.447524060199498</x:v>
@@ -1848,19 +1831,19 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A5" s="3" t="s">
-        <x:v>227</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="F5">
         <x:v>37.4444172059004</x:v>
@@ -1871,19 +1854,19 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A6" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F6">
         <x:v>37.439140760562097</x:v>
@@ -1894,19 +1877,19 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A7" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>159</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F7">
         <x:v>37.439654117607503</x:v>
@@ -1917,19 +1900,19 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A8" s="3" t="s">
-        <x:v>196</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F8">
         <x:v>37.447497932590402</x:v>
@@ -1940,19 +1923,19 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A9" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>164</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>37.4370981790032</x:v>
@@ -1963,19 +1946,19 @@
     </x:row>
     <x:row r="10" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A10" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>37.442450802593598</x:v>
@@ -1986,19 +1969,19 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A11" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F11">
         <x:v>37.440203699999998</x:v>
@@ -2009,19 +1992,19 @@
     </x:row>
     <x:row r="12" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A12" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F12">
         <x:v>37.439262473807098</x:v>
@@ -2032,19 +2015,19 @@
     </x:row>
     <x:row r="13" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A13" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F13">
         <x:v>37.4440801889331</x:v>
@@ -2055,19 +2038,19 @@
     </x:row>
     <x:row r="14" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A14" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F14">
         <x:v>37.431722871687697</x:v>
@@ -2078,19 +2061,19 @@
     </x:row>
     <x:row r="15" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A15" s="3" t="s">
-        <x:v>237</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F15">
         <x:v>37.446756841770203</x:v>
@@ -2101,19 +2084,19 @@
     </x:row>
     <x:row r="16" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A16" s="3" t="s">
-        <x:v>234</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F16">
         <x:v>37.439467125902802</x:v>
@@ -2124,19 +2107,19 @@
     </x:row>
     <x:row r="17" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A17" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F17">
         <x:v>37.436520158622002</x:v>
@@ -2147,19 +2130,19 @@
     </x:row>
     <x:row r="18" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A18" s="3" t="s">
-        <x:v>233</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F18">
         <x:v>37.437470952943301</x:v>
@@ -2170,19 +2153,19 @@
     </x:row>
     <x:row r="19" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A19" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F19">
         <x:v>37.437470952943301</x:v>
@@ -2193,19 +2176,19 @@
     </x:row>
     <x:row r="20" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A20" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F20">
         <x:v>37.415730984604401</x:v>
@@ -2216,19 +2199,19 @@
     </x:row>
     <x:row r="21" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A21" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F21">
         <x:v>37.449990132468002</x:v>
@@ -2239,19 +2222,19 @@
     </x:row>
     <x:row r="22" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A22" s="3" t="s">
-        <x:v>249</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>37.4370981790032</x:v>
@@ -2262,19 +2245,19 @@
     </x:row>
     <x:row r="23" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A23" s="3" t="s">
-        <x:v>200</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="F23">
         <x:v>37.446258234266701</x:v>
@@ -2285,19 +2268,19 @@
     </x:row>
     <x:row r="24" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A24" s="3" t="s">
-        <x:v>248</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>222</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F24">
         <x:v>37.436555875625103</x:v>
@@ -2308,19 +2291,19 @@
     </x:row>
     <x:row r="25" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A25" s="3" t="s">
-        <x:v>251</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>156</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F25">
         <x:v>37.435910670723203</x:v>
@@ -2331,19 +2314,19 @@
     </x:row>
     <x:row r="26" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A26" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>143</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F26">
         <x:v>37.433101325125101</x:v>
@@ -2354,19 +2337,19 @@
     </x:row>
     <x:row r="27" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A27" s="3" t="s">
-        <x:v>194</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C27" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F27">
         <x:v>37.435575200000002</x:v>
@@ -2377,19 +2360,19 @@
     </x:row>
     <x:row r="28" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A28" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C28" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F28">
         <x:v>37.436520158622002</x:v>
@@ -2400,19 +2383,19 @@
     </x:row>
     <x:row r="29" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A29" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C29" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F29">
         <x:v>37.435539800000001</x:v>
@@ -2421,1176 +2404,1153 @@
         <x:v>126.79114420000001</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:7" ht="13.19999999999999928946">
+    <x:row r="30" spans="1:7" customFormat="1" ht="13.19999999999999928946">
       <x:c r="A30" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C30" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F30">
-        <x:v>37.446271856574498</x:v>
+        <x:v>37.441218999999997</x:v>
       </x:c>
       <x:c r="G30">
-        <x:v>126.788781442071</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7" customFormat="1" ht="13.19999999999999928946">
+        <x:v>126.79591720000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A31" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C31" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>221</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F31">
-        <x:v>37.441218999999997</x:v>
+        <x:v>37.379756994823801</x:v>
       </x:c>
       <x:c r="G31">
-        <x:v>126.79591720000001</x:v>
+        <x:v>126.780655231343</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A32" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>161</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F32">
-        <x:v>37.379756994823801</x:v>
+        <x:v>37.380935743665098</x:v>
       </x:c>
       <x:c r="G32">
-        <x:v>126.780655231343</x:v>
+        <x:v>126.800838255491</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A33" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>147</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F33">
-        <x:v>37.380935743665098</x:v>
+        <x:v>37.393987258770103</x:v>
       </x:c>
       <x:c r="G33">
-        <x:v>126.800838255491</x:v>
+        <x:v>126.80502098617799</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A34" s="3" t="s">
-        <x:v>258</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F34">
-        <x:v>37.393987258770103</x:v>
+        <x:v>37.377924598191797</x:v>
       </x:c>
       <x:c r="G34">
-        <x:v>126.80502098617799</x:v>
+        <x:v>126.789234977478</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A35" s="3" t="s">
-        <x:v>211</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F35">
-        <x:v>37.377924598191797</x:v>
+        <x:v>37.383095058258597</x:v>
       </x:c>
       <x:c r="G35">
-        <x:v>126.789234977478</x:v>
+        <x:v>126.793439976225</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A36" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C36" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C36" s="4" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F36">
-        <x:v>37.383095058258597</x:v>
+        <x:v>37.3681299</x:v>
       </x:c>
       <x:c r="G36">
-        <x:v>126.793439976225</x:v>
+        <x:v>126.8114073</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A37" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C37" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F37">
-        <x:v>37.3681299</x:v>
+        <x:v>37.3797719285173</x:v>
       </x:c>
       <x:c r="G37">
-        <x:v>126.8114073</x:v>
+        <x:v>126.78044845216699</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A38" s="3" t="s">
-        <x:v>232</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C38" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>168</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F38">
-        <x:v>37.3797719285173</x:v>
+        <x:v>37.367986885096599</x:v>
       </x:c>
       <x:c r="G38">
-        <x:v>126.78044845216699</x:v>
+        <x:v>126.812257433445</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A39" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F39">
-        <x:v>37.367986885096599</x:v>
+        <x:v>37.3802217702235</x:v>
       </x:c>
       <x:c r="G39">
-        <x:v>126.812257433445</x:v>
+        <x:v>126.78018496540599</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A40" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C40" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D40" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E40" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F40">
-        <x:v>37.3802217702235</x:v>
+        <x:v>37.368047900000001</x:v>
       </x:c>
       <x:c r="G40">
-        <x:v>126.78018496540599</x:v>
+        <x:v>126.8117333</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A41" s="3" t="s">
-        <x:v>189</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C41" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D41" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E41" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41">
-        <x:v>37.368047900000001</x:v>
+        <x:v>37.373484639470199</x:v>
       </x:c>
       <x:c r="G41">
-        <x:v>126.8117333</x:v>
+        <x:v>126.790663834062</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A42" s="3" t="s">
-        <x:v>231</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C42" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D42" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E42" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F42">
-        <x:v>37.373484639470199</x:v>
+        <x:v>37.398895451269198</x:v>
       </x:c>
       <x:c r="G42">
-        <x:v>126.790663834062</x:v>
+        <x:v>126.800842012567</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A43" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C43" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D43" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E43" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F43">
-        <x:v>37.398895451269198</x:v>
+        <x:v>37.3780517</x:v>
       </x:c>
       <x:c r="G43">
-        <x:v>126.800842012567</x:v>
+        <x:v>126.7851359</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A44" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B44" s="2" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C44" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D44" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="B44" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C44" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D44" s="3" t="s">
-        <x:v>152</x:v>
-      </x:c>
       <x:c r="E44" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F44">
-        <x:v>37.3780517</x:v>
+        <x:v>37.393291300000001</x:v>
       </x:c>
       <x:c r="G44">
-        <x:v>126.7851359</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:7" ht="13.19999999999999928946">
-      <x:c r="A45" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>126.8054911</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7" customFormat="1" ht="13.19999999999999928946">
+      <x:c r="A45" s="7" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C45" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E45" s="3" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F45">
+        <x:v>37.377511200000001</x:v>
+      </x:c>
+      <x:c r="G45">
+        <x:v>126.7897158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7" ht="13.19999999999999928946">
+      <x:c r="A46" s="3" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B46" s="2" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C46" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D46" s="3" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F45">
-        <x:v>37.393291300000001</x:v>
-      </x:c>
-      <x:c r="G45">
-        <x:v>126.8054911</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7" customFormat="1" ht="13.19999999999999928946">
-      <x:c r="A46" s="7" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B46" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C46" s="4" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D46" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E46" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F46">
-        <x:v>37.377511200000001</x:v>
+        <x:v>37.343853763697801</x:v>
       </x:c>
       <x:c r="G46">
-        <x:v>126.7897158</x:v>
+        <x:v>126.78488703044</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A47" s="3" t="s">
-        <x:v>229</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B47" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C47" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D47" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E47" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F47">
-        <x:v>37.343853763697801</x:v>
+        <x:v>37.3391834476597</x:v>
       </x:c>
       <x:c r="G47">
-        <x:v>126.78488703044</x:v>
+        <x:v>126.74505684064501</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A48" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B48" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C48" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>165</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E48" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F48">
-        <x:v>37.3391834476597</x:v>
+        <x:v>37.348040523451701</x:v>
       </x:c>
       <x:c r="G48">
-        <x:v>126.74505684064501</x:v>
+        <x:v>126.761281592611</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A49" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B49" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C49" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E49" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F49">
-        <x:v>37.348040523451701</x:v>
+        <x:v>37.363216527590602</x:v>
       </x:c>
       <x:c r="G49">
-        <x:v>126.761281592611</x:v>
+        <x:v>126.73038793366599</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A50" s="3" t="s">
-        <x:v>230</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F50">
-        <x:v>37.363216527590602</x:v>
+        <x:v>37.3449460010808</x:v>
       </x:c>
       <x:c r="G50">
-        <x:v>126.73038793366599</x:v>
+        <x:v>126.78454647391</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A51" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D51" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F51">
-        <x:v>37.3449460010808</x:v>
+        <x:v>37.344975648325899</x:v>
       </x:c>
       <x:c r="G51">
-        <x:v>126.78454647391</x:v>
+        <x:v>126.691667263957</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A52" s="3" t="s">
-        <x:v>181</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D52" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F52">
-        <x:v>37.344975648325899</x:v>
+        <x:v>37.363914399999999</x:v>
       </x:c>
       <x:c r="G52">
-        <x:v>126.691667263957</x:v>
+        <x:v>126.7313666</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A53" s="3" t="s">
-        <x:v>198</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C53" s="3" t="s">
-        <x:v>193</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C53" s="4" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D53" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>122</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F53">
-        <x:v>37.363914399999999</x:v>
+        <x:v>37.347775104464098</x:v>
       </x:c>
       <x:c r="G53">
-        <x:v>126.7313666</x:v>
+        <x:v>126.74652330961401</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A54" s="3" t="s">
-        <x:v>185</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C54" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C54" s="3" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D54" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F54">
-        <x:v>37.347775104464098</x:v>
+        <x:v>37.340606096953202</x:v>
       </x:c>
       <x:c r="G54">
-        <x:v>126.74652330961401</x:v>
+        <x:v>126.785184851083</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A55" s="3" t="s">
-        <x:v>176</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C55" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C55" s="4" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D55" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E55" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F55">
-        <x:v>37.340606096953202</x:v>
+        <x:v>37.354204055025598</x:v>
       </x:c>
       <x:c r="G55">
-        <x:v>126.785184851083</x:v>
+        <x:v>126.731510609651</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A56" s="3" t="s">
-        <x:v>241</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C56" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D56" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E56" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F56">
-        <x:v>37.354204055025598</x:v>
+        <x:v>37.351623224076903</x:v>
       </x:c>
       <x:c r="G56">
-        <x:v>126.731510609651</x:v>
+        <x:v>126.741285900721</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A57" s="3" t="s">
-        <x:v>254</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C57" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D57" s="3" t="s">
-        <x:v>192</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E57" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F57">
-        <x:v>37.351623224076903</x:v>
+        <x:v>37.356434831380703</x:v>
       </x:c>
       <x:c r="G57">
-        <x:v>126.741285900721</x:v>
+        <x:v>126.735558097655</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A58" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B58" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C58" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E58" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F58">
-        <x:v>37.356434831380703</x:v>
+        <x:v>37.3479288939809</x:v>
       </x:c>
       <x:c r="G58">
-        <x:v>126.735558097655</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:7" ht="13.19999999999999928946">
+        <x:v>126.78274549352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:7" customFormat="1" ht="13.19999999999999928946">
       <x:c r="A59" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B59" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C59" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D59" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E59" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F59">
-        <x:v>37.3479288939809</x:v>
+        <x:v>37.346961604063502</x:v>
       </x:c>
       <x:c r="G59">
-        <x:v>126.78274549352</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:7" customFormat="1" ht="13.19999999999999928946">
+        <x:v>37.346961604063502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A60" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B60" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C60" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C60" s="3" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D60" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E60" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F60">
-        <x:v>37.346961604063502</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G60">
-        <x:v>37.346961604063502</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A61" s="3" t="s">
-        <x:v>190</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B61" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D61" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E61" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F61">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.3821400563113</x:v>
       </x:c>
       <x:c r="G61">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.73471959141401</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A62" s="3" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B62" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C62" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D62" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E62" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F62">
-        <x:v>37.3821400563113</x:v>
+        <x:v>37.374597699315999</x:v>
       </x:c>
       <x:c r="G62">
-        <x:v>126.73471959141401</x:v>
+        <x:v>126.73340139468</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A63" s="3" t="s">
-        <x:v>226</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B63" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C63" s="3" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D63" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D63" s="5" t="s">
+        <x:v>246</x:v>
       </x:c>
       <x:c r="E63" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="F63">
-        <x:v>37.374597699315999</x:v>
+        <x:v>37.388653900000001</x:v>
       </x:c>
       <x:c r="G63">
-        <x:v>126.73340139468</x:v>
+        <x:v>126.7383327</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A64" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B64" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C64" s="3" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D64" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D64" s="3" t="s">
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E64" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F64">
-        <x:v>37.388653900000001</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G64">
-        <x:v>126.7383327</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A65" s="3" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B65" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D65" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E65" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F65">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.387693446987001</x:v>
       </x:c>
       <x:c r="G65">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.742398261746</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A66" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B66" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D66" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E66" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F66">
-        <x:v>37.387693446987001</x:v>
+        <x:v>37.374245882999702</x:v>
       </x:c>
       <x:c r="G66">
-        <x:v>126.742398261746</x:v>
+        <x:v>126.733976285898</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A67" s="3" t="s">
-        <x:v>180</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D67" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E67" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F67">
-        <x:v>37.374245882999702</x:v>
+        <x:v>37.390598400000002</x:v>
       </x:c>
       <x:c r="G67">
-        <x:v>126.733976285898</x:v>
+        <x:v>126.73915220000001</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A68" s="3" t="s">
-        <x:v>203</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D68" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E68" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F68">
-        <x:v>37.390598400000002</x:v>
+        <x:v>37.374066672514303</x:v>
       </x:c>
       <x:c r="G68">
-        <x:v>126.73915220000001</x:v>
+        <x:v>126.734258152593</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A69" s="3" t="s">
-        <x:v>206</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B69" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C69" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D69" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E69" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F69">
-        <x:v>37.374066672514303</x:v>
+        <x:v>37.389604498273997</x:v>
       </x:c>
       <x:c r="G69">
-        <x:v>126.734258152593</x:v>
+        <x:v>126.738166472757</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A70" s="3" t="s">
-        <x:v>253</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B70" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C70" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D70" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E70" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F70">
-        <x:v>37.389604498273997</x:v>
+        <x:v>37.3748395</x:v>
       </x:c>
       <x:c r="G70">
-        <x:v>126.738166472757</x:v>
+        <x:v>126.7329841</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A71" s="3" t="s">
-        <x:v>245</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B71" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C71" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C71" s="4" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D71" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E71" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F71">
-        <x:v>37.3748395</x:v>
+        <x:v>37.377342450217498</x:v>
       </x:c>
       <x:c r="G71">
-        <x:v>126.7329841</x:v>
+        <x:v>126.727496126419</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A72" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B72" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C72" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D72" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E72" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F72">
-        <x:v>37.377342450217498</x:v>
+        <x:v>37.373859521094502</x:v>
       </x:c>
       <x:c r="G72">
-        <x:v>126.727496126419</x:v>
+        <x:v>126.734576357199</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A73" s="3" t="s">
-        <x:v>246</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B73" s="2" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C73" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D73" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E73" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F73">
-        <x:v>37.373859521094502</x:v>
+        <x:v>37.3821400563113</x:v>
       </x:c>
       <x:c r="G73">
-        <x:v>126.734576357199</x:v>
+        <x:v>126.73471959141401</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A74" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B74" s="2" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C74" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D74" s="3" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B74" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D74" s="3" t="s">
-        <x:v>173</x:v>
-      </x:c>
       <x:c r="E74" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F74">
-        <x:v>37.3821400563113</x:v>
+        <x:v>37.382286000000001</x:v>
       </x:c>
       <x:c r="G74">
-        <x:v>126.73471959141401</x:v>
+        <x:v>126.7353871</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A75" s="3" t="s">
-        <x:v>205</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B75" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C75" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D75" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E75" s="3" t="s">
-        <x:v>107</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F75">
-        <x:v>37.382286000000001</x:v>
+        <x:v>37.370413200000002</x:v>
       </x:c>
       <x:c r="G75">
-        <x:v>126.7353871</x:v>
+        <x:v>126.7339216</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A76" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B76" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C76" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D76" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E76" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F76">
-        <x:v>37.370413200000002</x:v>
+        <x:v>37.393791434243496</x:v>
       </x:c>
       <x:c r="G76">
-        <x:v>126.7339216</x:v>
+        <x:v>126.73934252606</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A77" s="3" t="s">
-        <x:v>197</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C77" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D77" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E77" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F77">
-        <x:v>37.393791434243496</x:v>
+        <x:v>37.3705044199436</x:v>
       </x:c>
       <x:c r="G77">
-        <x:v>126.73934252606</x:v>
+        <x:v>126.72797063404801</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A78" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B78" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C78" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C78" s="3" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D78" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E78" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F78">
-        <x:v>37.3705044199436</x:v>
+        <x:v>37.381190099999998</x:v>
       </x:c>
       <x:c r="G78">
-        <x:v>126.72797063404801</x:v>
+        <x:v>126.86278299999999</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="13.19999999999999928946">
       <x:c r="A79" s="3" t="s">
-        <x:v>235</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B79" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C79" s="3" t="s">
-        <x:v>202</x:v>
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C79" s="4" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D79" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E79" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F79">
-        <x:v>37.381190099999998</x:v>
+        <x:v>37.382772633833603</x:v>
       </x:c>
       <x:c r="G79">
-        <x:v>126.86278299999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:7" ht="13.19999999999999928946">
-      <x:c r="A80" s="3" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="B80" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C80" s="4" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D80" s="3" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="E80" s="3" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F80">
-        <x:v>37.382772633833603</x:v>
-      </x:c>
-      <x:c r="G80">
         <x:v>126.86169881025801</x:v>
       </x:c>
     </x:row>
